--- a/employee_information_forms/030_employee_absenteeism_form--employee_information_forms.xlsx
+++ b/employee_information_forms/030_employee_absenteeism_form--employee_information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -784,8 +784,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,12 +813,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'sick_leave'}</t>
+          <t>sick_leave</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Sick leave'}</t>
+          <t>Sick leave</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'vacation'}</t>
+          <t>vacation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Vacation'}</t>
+          <t>Vacation</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'personal_reasons'}</t>
+          <t>personal_reasons</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Personal reasons'}</t>
+          <t>Personal reasons</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'doctor’s_visit'}</t>
+          <t>doctor’s_visit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Doctor’s visit'}</t>
+          <t>Doctor’s visit</t>
         </is>
       </c>
     </row>
